--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -609,7 +609,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1534,7 +1534,7 @@
         <is>
           <t>2号屋
 12073呎 (4+房)
-(已售)
+(24年-10月)
 $8.45亿
 $69,991/呎</t>
         </is>
@@ -1543,7 +1543,7 @@
         <is>
           <t>3号屋
 9694呎 (4+房)
-(已售)
+(24年-08月)
 $7.17亿
 $74,000/呎</t>
         </is>
@@ -1552,7 +1552,7 @@
         <is>
           <t>5号屋
 6695呎 (4+房)
-(已售)
+(24年-03月)
 $4.98亿
 $74,400/呎</t>
         </is>
@@ -1561,7 +1561,7 @@
         <is>
           <t>6号屋
 9550呎 (4+房)
-(已售)
+(25年-10月)
 $5.79亿
 $60,623/呎</t>
         </is>
@@ -1570,7 +1570,7 @@
         <is>
           <t>7号屋
 8032呎 (4+房)
-(已售)
+(22年-07月)
 $8.70亿
 $108,347/呎</t>
         </is>
@@ -1586,7 +1586,7 @@
         <is>
           <t>8号屋
 2746呎 (4+房)
-(已售)
+(24年-05月)
 $2.60亿
 $94,670/呎</t>
         </is>
@@ -1595,7 +1595,7 @@
         <is>
           <t>9号屋
 3727呎 (4+房)
-(已售)
+(26年-01月)
 $2.25亿
 $60,263/呎</t>
         </is>
@@ -1604,7 +1604,7 @@
         <is>
           <t>10号屋
 4853呎 (4+房)
-(已售)
+(26年-01月)
 $2.92亿
 $60,264/呎</t>
         </is>
@@ -1613,7 +1613,7 @@
         <is>
           <t>11号屋
 4759呎 (4+房)
-(已售)
+(22年-08月)
 $4.35亿
 $91,406/呎</t>
         </is>
@@ -1622,7 +1622,7 @@
         <is>
           <t>12号屋
 4696呎 (4+房)
-(已售)
+(24年-07月)
 $3.20亿
 $68,177/呎</t>
         </is>
@@ -1631,7 +1631,7 @@
         <is>
           <t>15号屋
 4696呎 (4+房)
-(已售)
+(26年-01月)
 $2.90亿
 $61,725/呎</t>
         </is>

--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,22 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -223,13 +239,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -626,7 +626,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -686,6 +690,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -736,6 +760,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -782,6 +826,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -828,6 +892,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -874,6 +958,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -920,6 +1024,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -966,6 +1090,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1012,6 +1156,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1058,6 +1222,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1104,6 +1288,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1150,6 +1354,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1196,6 +1420,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1242,6 +1486,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1292,6 +1556,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1342,6 +1626,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1392,13 +1696,33 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1550,7 +1874,7 @@
         <is>
           <t>2号屋
 12073呎 (4+房)
-(24年-10月)
+(24年-10月-31日)
 $8.45亿
 $69,991/呎</t>
         </is>
@@ -1559,7 +1883,7 @@
         <is>
           <t>3号屋
 9694呎 (4+房)
-(24年-08月)
+(24年-08月-11日)
 $7.17亿
 $74,000/呎</t>
         </is>
@@ -1568,7 +1892,7 @@
         <is>
           <t>5号屋
 6695呎 (4+房)
-(24年-03月)
+(24年-03月-04日)
 $4.98亿
 $74,400/呎</t>
         </is>
@@ -1577,7 +1901,7 @@
         <is>
           <t>6号屋
 9550呎 (4+房)
-(25年-10月)
+(25年-10月-15日)
 $5.79亿
 $60,623/呎</t>
         </is>
@@ -1586,7 +1910,7 @@
         <is>
           <t>7号屋
 8032呎 (4+房)
-(22年-07月)
+(22年-07月-21日)
 $8.70亿
 $108,347/呎</t>
         </is>
@@ -1602,7 +1926,7 @@
         <is>
           <t>8号屋
 2746呎 (4+房)
-(24年-05月)
+(24年-05月-21日)
 $2.60亿
 $94,670/呎</t>
         </is>
@@ -1611,7 +1935,7 @@
         <is>
           <t>9号屋
 3727呎 (4+房)
-(26年-01月)
+(26年-01月-26日)
 $2.25亿
 $60,263/呎</t>
         </is>
@@ -1620,7 +1944,7 @@
         <is>
           <t>10号屋
 4853呎 (4+房)
-(26年-01月)
+(26年-01月-26日)
 $2.92亿
 $60,264/呎</t>
         </is>
@@ -1629,7 +1953,7 @@
         <is>
           <t>11号屋
 4759呎 (4+房)
-(22年-08月)
+(22年-08月-07日)
 $4.35亿
 $91,406/呎</t>
         </is>
@@ -1638,7 +1962,7 @@
         <is>
           <t>12号屋
 4696呎 (4+房)
-(24年-07月)
+(24年-07月-29日)
 $3.20亿
 $68,177/呎</t>
         </is>
@@ -1647,7 +1971,7 @@
         <is>
           <t>15号屋
 4696呎 (4+房)
-(26年-01月)
+(26年-01月-06日)
 $2.90亿
 $61,725/呎</t>
         </is>

--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -1874,7 +1874,7 @@
         <is>
           <t>2号屋
 12073呎 (4+房)
-(24年-10月-31日)
+(24年-10月)
 $8.45亿
 $69,991/呎</t>
         </is>
@@ -1883,7 +1883,7 @@
         <is>
           <t>3号屋
 9694呎 (4+房)
-(24年-08月-11日)
+(24年-08月)
 $7.17亿
 $74,000/呎</t>
         </is>
@@ -1892,7 +1892,7 @@
         <is>
           <t>5号屋
 6695呎 (4+房)
-(24年-03月-04日)
+(24年-03月)
 $4.98亿
 $74,400/呎</t>
         </is>
@@ -1901,7 +1901,7 @@
         <is>
           <t>6号屋
 9550呎 (4+房)
-(25年-10月-15日)
+(25年-10月)
 $5.79亿
 $60,623/呎</t>
         </is>
@@ -1910,7 +1910,7 @@
         <is>
           <t>7号屋
 8032呎 (4+房)
-(22年-07月-21日)
+(22年-07月)
 $8.70亿
 $108,347/呎</t>
         </is>
@@ -1926,7 +1926,7 @@
         <is>
           <t>8号屋
 2746呎 (4+房)
-(24年-05月-21日)
+(24年-05月)
 $2.60亿
 $94,670/呎</t>
         </is>
@@ -1935,7 +1935,7 @@
         <is>
           <t>9号屋
 3727呎 (4+房)
-(26年-01月-26日)
+(26年-01月)
 $2.25亿
 $60,263/呎</t>
         </is>
@@ -1944,7 +1944,7 @@
         <is>
           <t>10号屋
 4853呎 (4+房)
-(26年-01月-26日)
+(26年-01月)
 $2.92亿
 $60,264/呎</t>
         </is>
@@ -1953,7 +1953,7 @@
         <is>
           <t>11号屋
 4759呎 (4+房)
-(22年-08月-07日)
+(22年-08月)
 $4.35亿
 $91,406/呎</t>
         </is>
@@ -1962,7 +1962,7 @@
         <is>
           <t>12号屋
 4696呎 (4+房)
-(24年-07月-29日)
+(24年-07月)
 $3.20亿
 $68,177/呎</t>
         </is>
@@ -1971,7 +1971,7 @@
         <is>
           <t>15号屋
 4696呎 (4+房)
-(26年-01月-06日)
+(26年-01月)
 $2.90亿
 $61,725/呎</t>
         </is>

--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -1874,7 +1874,7 @@
         <is>
           <t>2号屋
 12073呎 (4+房)
-(24年-10月)
+(24年-10月-31日)
 $8.45亿
 $69,991/呎</t>
         </is>
@@ -1883,7 +1883,7 @@
         <is>
           <t>3号屋
 9694呎 (4+房)
-(24年-08月)
+(24年-08月-11日)
 $7.17亿
 $74,000/呎</t>
         </is>
@@ -1892,7 +1892,7 @@
         <is>
           <t>5号屋
 6695呎 (4+房)
-(24年-03月)
+(24年-03月-04日)
 $4.98亿
 $74,400/呎</t>
         </is>
@@ -1901,7 +1901,7 @@
         <is>
           <t>6号屋
 9550呎 (4+房)
-(25年-10月)
+(25年-10月-15日)
 $5.79亿
 $60,623/呎</t>
         </is>
@@ -1910,7 +1910,7 @@
         <is>
           <t>7号屋
 8032呎 (4+房)
-(22年-07月)
+(22年-07月-21日)
 $8.70亿
 $108,347/呎</t>
         </is>
@@ -1926,7 +1926,7 @@
         <is>
           <t>8号屋
 2746呎 (4+房)
-(24年-05月)
+(24年-05月-21日)
 $2.60亿
 $94,670/呎</t>
         </is>
@@ -1935,7 +1935,7 @@
         <is>
           <t>9号屋
 3727呎 (4+房)
-(26年-01月)
+(26年-01月-26日)
 $2.25亿
 $60,263/呎</t>
         </is>
@@ -1944,7 +1944,7 @@
         <is>
           <t>10号屋
 4853呎 (4+房)
-(26年-01月)
+(26年-01月-26日)
 $2.92亿
 $60,264/呎</t>
         </is>
@@ -1953,7 +1953,7 @@
         <is>
           <t>11号屋
 4759呎 (4+房)
-(22年-08月)
+(22年-08月-07日)
 $4.35亿
 $91,406/呎</t>
         </is>
@@ -1962,7 +1962,7 @@
         <is>
           <t>12号屋
 4696呎 (4+房)
-(24年-07月)
+(24年-07月-29日)
 $3.20亿
 $68,177/呎</t>
         </is>
@@ -1971,7 +1971,7 @@
         <is>
           <t>15号屋
 4696呎 (4+房)
-(26年-01月)
+(26年-01月-06日)
 $2.90亿
 $61,725/呎</t>
         </is>
